--- a/sheets/대금율보/검수/진도아리랑 (b1_130_1).xlsx
+++ b/sheets/대금율보/검수/진도아리랑 (b1_130_1).xlsx
@@ -3780,8 +3780,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
@@ -3791,8 +3790,7 @@
       </c>
       <c r="D8" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢∧)
-‹</t>
+          <t xml:space="preserve">潢∧)</t>
         </is>
       </c>
       <c r="E8" s="28" t="inlineStr">
@@ -3802,8 +3800,7 @@
       </c>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="G8" s="24" t="inlineStr">
@@ -3815,8 +3812,7 @@
         <is>
           <t xml:space="preserve">淋
 浹
-汰
-‹</t>
+汰</t>
         </is>
       </c>
       <c r="I8" s="24" t="inlineStr">
@@ -3828,8 +3824,7 @@
         <is>
           <t xml:space="preserve">浹
 汰
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="K8" s="24" t="inlineStr">
@@ -3839,8 +3834,7 @@
       </c>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="M8" s="24" t="inlineStr">

--- a/sheets/대금율보/검수/진도아리랑 (b1_130_1).xlsx
+++ b/sheets/대금율보/검수/진도아리랑 (b1_130_1).xlsx
@@ -3413,24 +3413,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="11.63" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="11.63" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="11.63" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="11.63" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="11.63" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="11.63" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="60.61" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="90.2" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="90.2" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="90.2" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="90.2" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="90.2" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="90.2" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="90.2" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="90.2" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="90.2" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="90.2" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="90.2" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="M13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="90.2" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4224,6 +4224,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
 </worksheet>
 </file>